--- a/converted_files/837/837P-all-fields.xlsx
+++ b/converted_files/837/837P-all-fields.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b50fb</t>
+          <t>69e82c69836d7d05c9a0592d</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="BM2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="BN2" s="3" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="CN2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="CO2" s="4" t="n">
@@ -2227,7 +2227,9 @@
       <c r="CW2" s="4" t="n">
         <v>38360.0</v>
       </c>
-      <c r="CX2"/>
+      <c r="CX2" s="4" t="n">
+        <v>38473.0</v>
+      </c>
       <c r="CY2" s="4" t="n">
         <v>38511.0</v>
       </c>
@@ -2245,7 +2247,7 @@
       </c>
       <c r="DD2" s="3" t="inlineStr">
         <is>
-          <t>ServiceAuthorizationExceptionCode</t>
+          <t>7</t>
         </is>
       </c>
       <c r="DE2" s="3" t="inlineStr">
@@ -2747,12 +2749,12 @@
       <c r="IM2"/>
       <c r="IN2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="IO2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="IP2" s="3" t="inlineStr">
@@ -2762,7 +2764,7 @@
       </c>
       <c r="IQ2" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>0</t>
         </is>
       </c>
       <c r="IR2" s="4" t="n">
@@ -2995,7 +2997,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b50fb</t>
+          <t>69e82c69836d7d05c9a0592d</t>
         </is>
       </c>
       <c r="B3"/>
@@ -3380,7 +3382,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b50fb</t>
+          <t>69e82c69836d7d05c9a0592d</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3656,10 +3658,10 @@
       <c r="IP4"/>
       <c r="IQ4"/>
       <c r="IR4" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="IS4" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="IT4"/>
       <c r="IU4"/>
@@ -3765,7 +3767,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b50fb</t>
+          <t>69e82c69836d7d05c9a0592d</t>
         </is>
       </c>
       <c r="B5"/>
@@ -4063,8 +4065,14 @@
           <t>01234567891</t>
         </is>
       </c>
-      <c r="JG5"/>
-      <c r="JH5"/>
+      <c r="JG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="JH5" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
       <c r="JI5"/>
       <c r="JJ5"/>
       <c r="JK5"/>

--- a/converted_files/837/837P-all-fields.xlsx
+++ b/converted_files/837/837P-all-fields.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b50fb</t>
+          <t>69efef06ad4799caa7f5e58e</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="BM2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="BN2" s="3" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="CN2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="CO2" s="4" t="n">
@@ -2227,7 +2227,9 @@
       <c r="CW2" s="4" t="n">
         <v>38360.0</v>
       </c>
-      <c r="CX2"/>
+      <c r="CX2" s="4" t="n">
+        <v>38473.0</v>
+      </c>
       <c r="CY2" s="4" t="n">
         <v>38511.0</v>
       </c>
@@ -2245,7 +2247,7 @@
       </c>
       <c r="DD2" s="3" t="inlineStr">
         <is>
-          <t>ServiceAuthorizationExceptionCode</t>
+          <t>7</t>
         </is>
       </c>
       <c r="DE2" s="3" t="inlineStr">
@@ -2747,12 +2749,12 @@
       <c r="IM2"/>
       <c r="IN2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="IO2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="IP2" s="3" t="inlineStr">
@@ -2762,7 +2764,7 @@
       </c>
       <c r="IQ2" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>0</t>
         </is>
       </c>
       <c r="IR2" s="4" t="n">
@@ -2995,7 +2997,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b50fb</t>
+          <t>69efef06ad4799caa7f5e58e</t>
         </is>
       </c>
       <c r="B3"/>
@@ -3380,7 +3382,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b50fb</t>
+          <t>69efef06ad4799caa7f5e58e</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3656,10 +3658,10 @@
       <c r="IP4"/>
       <c r="IQ4"/>
       <c r="IR4" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="IS4" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="IT4"/>
       <c r="IU4"/>
@@ -3765,7 +3767,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6918d0587f059d7aab1b50fb</t>
+          <t>69efef06ad4799caa7f5e58e</t>
         </is>
       </c>
       <c r="B5"/>
@@ -4063,8 +4065,14 @@
           <t>01234567891</t>
         </is>
       </c>
-      <c r="JG5"/>
-      <c r="JH5"/>
+      <c r="JG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="JH5" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
       <c r="JI5"/>
       <c r="JJ5"/>
       <c r="JK5"/>

--- a/converted_files/837/837P-all-fields.xlsx
+++ b/converted_files/837/837P-all-fields.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0592d</t>
+          <t>6a04cb3c618f76c4f7b197de</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2997,7 +2997,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0592d</t>
+          <t>6a04cb3c618f76c4f7b197de</t>
         </is>
       </c>
       <c r="B3"/>
@@ -3382,7 +3382,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0592d</t>
+          <t>6a04cb3c618f76c4f7b197de</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3767,7 +3767,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a0592d</t>
+          <t>6a04cb3c618f76c4f7b197de</t>
         </is>
       </c>
       <c r="B5"/>

--- a/converted_files/837/837P-all-fields.xlsx
+++ b/converted_files/837/837P-all-fields.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b197de</t>
+          <t>6a04cc5c1ef26d534baf42ec</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2997,7 +2997,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b197de</t>
+          <t>6a04cc5c1ef26d534baf42ec</t>
         </is>
       </c>
       <c r="B3"/>
@@ -3382,7 +3382,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b197de</t>
+          <t>6a04cc5c1ef26d534baf42ec</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3767,7 +3767,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b197de</t>
+          <t>6a04cc5c1ef26d534baf42ec</t>
         </is>
       </c>
       <c r="B5"/>

--- a/converted_files/837/837P-all-fields.xlsx
+++ b/converted_files/837/837P-all-fields.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf42ec</t>
+          <t>6a0614dff8d6a2fc74349136</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2997,7 +2997,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf42ec</t>
+          <t>6a0614dff8d6a2fc74349136</t>
         </is>
       </c>
       <c r="B3"/>
@@ -3382,7 +3382,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf42ec</t>
+          <t>6a0614dff8d6a2fc74349136</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3767,7 +3767,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf42ec</t>
+          <t>6a0614dff8d6a2fc74349136</t>
         </is>
       </c>
       <c r="B5"/>

--- a/converted_files/837/837P-all-fields.xlsx
+++ b/converted_files/837/837P-all-fields.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349136</t>
+          <t>6a32cb6597613a0e49909816</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2997,7 +2997,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349136</t>
+          <t>6a32cb6597613a0e49909816</t>
         </is>
       </c>
       <c r="B3"/>
@@ -3382,7 +3382,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349136</t>
+          <t>6a32cb6597613a0e49909816</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3767,7 +3767,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a0614dff8d6a2fc74349136</t>
+          <t>6a32cb6597613a0e49909816</t>
         </is>
       </c>
       <c r="B5"/>
